--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:20+00:00</t>
+    <t>2023-05-10T08:50:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:38+00:00</t>
+    <t>2023-05-10T09:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:32+00:00</t>
+    <t>2023-05-10T09:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:57+00:00</t>
+    <t>2023-05-10T09:45:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:45:15+00:00</t>
+    <t>2023-05-10T09:50:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:50:54+00:00</t>
+    <t>2023-05-10T10:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:15:35+00:00</t>
+    <t>2023-05-10T10:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:16:16+00:00</t>
+    <t>2023-05-10T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:21+00:00</t>
+    <t>2023-05-10T11:05:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:55+00:00</t>
+    <t>2023-05-10T11:27:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:27:56+00:00</t>
+    <t>2023-05-10T11:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:35:39+00:00</t>
+    <t>2023-05-10T12:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:05+00:00</t>
+    <t>2023-05-10T12:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:34+00:00</t>
+    <t>2023-05-11T06:47:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:47:47+00:00</t>
+    <t>2023-05-11T06:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:48:00+00:00</t>
+    <t>2023-05-11T06:54:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:20+00:00</t>
+    <t>2023-05-11T06:54:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:25+00:00</t>
+    <t>2023-05-11T08:35:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:35:45+00:00</t>
+    <t>2023-05-11T08:41:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:41:43+00:00</t>
+    <t>2023-05-11T09:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:08:26+00:00</t>
+    <t>2023-05-11T09:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:17:12+00:00</t>
+    <t>2023-05-11T10:17:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:25+00:00</t>
+    <t>2023-05-11T10:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:56+00:00</t>
+    <t>2023-05-11T10:34:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:34:10+00:00</t>
+    <t>2023-05-11T10:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:41:58+00:00</t>
+    <t>2023-05-11T10:56:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:16+00:00</t>
+    <t>2023-05-11T10:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:44+00:00</t>
+    <t>2023-05-11T11:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:14:34+00:00</t>
+    <t>2023-05-11T11:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/device-for-testing</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/device-for-testing</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:21:30+00:00</t>
+    <t>2023-05-11T11:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:55:17+00:00</t>
+    <t>2023-05-11T12:03:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/device-for-testing</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/device-for-testing</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:03:20+00:00</t>
+    <t>2023-05-11T12:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:08:48+00:00</t>
+    <t>2023-05-11T12:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:16:35+00:00</t>
+    <t>2023-05-11T12:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:20:22+00:00</t>
+    <t>2023-05-11T12:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:21:18+00:00</t>
+    <t>2023-05-11T15:25:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:25:42+00:00</t>
+    <t>2023-05-11T15:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:26:02+00:00</t>
+    <t>2023-05-11T16:43:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:02+00:00</t>
+    <t>2023-05-11T16:43:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:55+00:00</t>
+    <t>2023-05-11T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:57:46+00:00</t>
+    <t>2023-05-11T16:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:58:30+00:00</t>
+    <t>2023-05-11T17:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:02+00:00</t>
+    <t>2023-05-11T17:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/device-for-testing</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/device-for-testing</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:30+00:00</t>
+    <t>2023-05-11T18:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:15:51+00:00</t>
+    <t>2023-05-11T18:16:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/device-for-testing</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/device-for-testing</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:16:31+00:00</t>
+    <t>2023-05-11T18:27:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:27:59+00:00</t>
+    <t>2023-05-11T18:29:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:29:46+00:00</t>
+    <t>2023-05-11T18:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:48:31+00:00</t>
+    <t>2023-05-11T18:54:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:54:41+00:00</t>
+    <t>2023-05-11T19:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:41:30+00:00</t>
+    <t>2023-05-11T19:42:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:42:15+00:00</t>
+    <t>2023-05-11T20:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:23:29+00:00</t>
+    <t>2023-05-11T20:24:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:24:51+00:00</t>
+    <t>2023-05-12T02:48:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:48:54+00:00</t>
+    <t>2023-05-12T02:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:49:37+00:00</t>
+    <t>2023-05-12T07:30:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:25+00:00</t>
+    <t>2023-05-12T07:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:35+00:00</t>
+    <t>2023-05-12T07:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:14+00:00</t>
+    <t>2023-05-12T07:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:30+00:00</t>
+    <t>2023-05-12T07:54:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:54:06+00:00</t>
+    <t>2023-05-12T07:55:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:55:51+00:00</t>
+    <t>2023-05-12T10:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:26:59+00:00</t>
+    <t>2023-05-12T10:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:27:50+00:00</t>
+    <t>2023-05-12T10:32:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:32:06+00:00</t>
+    <t>2023-05-12T10:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:40:31+00:00</t>
+    <t>2023-05-12T13:37:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:37:18+00:00</t>
+    <t>2023-05-12T13:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:51:30+00:00</t>
+    <t>2023-05-23T09:07:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:07:38+00:00</t>
+    <t>2023-05-23T09:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
